--- a/forras/csapat_nyilvantartas.xlsx
+++ b/forras/csapat_nyilvantartas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kochnorbert/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67A2C861-8F00-474B-BCA2-B7F1CC6B5952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45B96BD0-AEC0-FB41-B09B-822B2AB2F326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="600" windowWidth="16380" windowHeight="8200" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legenda" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Heti beosztás" sheetId="6" r:id="rId6"/>
     <sheet name="Éves összesítő" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5173" uniqueCount="638">
   <si>
     <t>Csapat nyilvántartó — használati útmutató</t>
   </si>
@@ -1962,13 +1962,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1994,8 +1999,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2080,6 +2092,12 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2093,36 +2111,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -6705,7 +6725,7 @@
       </c>
     </row>
     <row r="2" spans="1:366" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="21">
         <v>24009</v>
       </c>
       <c r="D2" s="18"/>
@@ -6762,17 +6782,23 @@
       <c r="FX2" s="18"/>
       <c r="GD2" s="18"/>
       <c r="GE2" s="18"/>
-      <c r="GF2" t="s">
-        <v>9</v>
-      </c>
-      <c r="GG2" t="s">
-        <v>9</v>
-      </c>
-      <c r="GH2" t="s">
-        <v>9</v>
-      </c>
       <c r="GK2" s="18"/>
       <c r="GL2" s="18"/>
+      <c r="GM2" t="s">
+        <v>9</v>
+      </c>
+      <c r="GN2" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="GO2" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="GP2" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="GQ2" s="22" t="s">
+        <v>9</v>
+      </c>
       <c r="GR2" s="18"/>
       <c r="GS2" s="18"/>
       <c r="GY2" s="18"/>
@@ -8471,7 +8497,7 @@
       <c r="MX17" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:NB17">
+  <conditionalFormatting sqref="B3:NB17 B2:GM2 GR2:NB2">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"SZ"</formula>
     </cfRule>
@@ -25168,7 +25194,7 @@
       </c>
       <c r="G2" s="20">
         <f>COUNTIF('Napi jelenlét 2026'!B2:NB2,"SZ")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" s="20">
         <f>COUNTIF('Napi jelenlét 2026'!B2:NB2,"B")</f>
